--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/payroll_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/payroll_timeline.xlsx
@@ -40,22 +40,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t/>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/307538032.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -67,7 +67,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -77,12 +77,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -94,7 +94,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -104,12 +104,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>179.83</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/CarlundCarla_RG424005125.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -121,7 +121,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -131,12 +131,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/CarlundCarla_RG424005157.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -148,22 +148,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t/>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t/>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Docutain Dokument.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -175,7 +175,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -185,12 +185,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>916.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Gutschrift 34-2024 Zahariev Martin 04.10.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -202,7 +202,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -212,12 +212,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>670.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/gutschrift 71 2025 zahariev Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -229,22 +229,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>517.65</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t/>
+          <t>435.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -256,12 +256,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -271,7 +271,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -288,7 +288,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -298,7 +298,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -315,7 +315,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -325,7 +325,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -337,22 +337,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t/>
+          <t>31.08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t/>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -364,7 +364,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t/>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -374,12 +374,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>1620.17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Martin Zahariev Gutschrift 55 08.03.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073-1.pdf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -391,7 +391,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2058-08</t>
+          <t/>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -401,12 +401,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>536.00</t>
+          <t>1620.17</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073.pdf</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -418,22 +418,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t/>
+          <t>895.36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -445,22 +445,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t/>
+          <t>546.15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/RE-53652_2024 20.09.2024 10_56_50.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -472,22 +472,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t/>
+          <t>812.26</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1620.17</t>
+          <t/>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rechnung RE211073-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -499,22 +499,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t/>
+          <t>0.20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1620.17</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rechnung RE211073.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>670.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rechnung_RE058675_11.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -553,22 +553,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>895.36</t>
+          <t>10499.90</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t/>
+          <t>10499.90</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -580,22 +580,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>546.15</t>
+          <t/>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t/>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -607,22 +607,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>812.26</t>
+          <t/>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t/>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -634,22 +634,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t/>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t/>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1709.48</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>148608.05</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>5245.59</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>532.95</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2024.eml::41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 02-2025.eml::46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -850,22 +850,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t/>
+          <t>11062.00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>11062.00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 03-2024.eml::41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 04-2024.eml::42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -904,7 +904,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>179.83</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 06-2024.eml::43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005125.pdf</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 07-2024.eml::43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005157.pdf</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2036-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>568.00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 09-2024.eml::44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2054-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>536.00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 10-2024.eml::45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1012,7 +1012,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2058-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>536.00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 11-2024.eml::45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1039,22 +1039,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>11062.00</t>
+          <t/>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>11062.00</t>
+          <t>536.00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/Accountings 12-2024.eml::46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>420.00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings012024.zip::40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1093,22 +1093,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10499.90</t>
+          <t/>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10499.90</t>
+          <t>504.00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings012024.zip::40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings112023.zip::39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>440.00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/accountings112023.zip::90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>101253.65</t>
+          <t>6960.00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdabrechnungmai2025.zip::gutschrift 66 Mai 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2789 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>148096.04</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdabrechnungseptember.zip::Gutschrift 31-2024 Zahariev Martin 30.09.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2794 Zahariev KFZ Miete.pdf</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::gutschrift 05.04. 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1545.27</t>
+          <t>7980.00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2766 Zahariev Hermes Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>280.00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>536.00</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1336,7 +1336,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdfwgutschriftrechnungen.zip::Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2814 zahariev bekleidung.pdf</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>440.00</t>
+          <t>1709.48</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1390,7 +1390,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>6960.00</t>
+          <t>148608.05</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2789 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>100833.17</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2794 Zahariev KFZ Miete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000826.pdf</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>45.00</t>
+          <t>28715.40</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgsundrechnungen052025.zip::Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000990.pdf</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>195225.85</t>
+          <t>5245.59</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10390.09</t>
+          <t>532.95</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1552,7 +1552,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>2137.23</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdgutschriftundrechnungen.zip::Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035414.pdf</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2137.23</t>
+          <t>511.46</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen012024350690382950.zip::Unternehmerabrechnung - VP 120-2400035414.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1606,7 +1606,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>511.46</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen012024350690382950.zip::Unternehmerabrechnung - VP 120-2400035649.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Docutain Dokument.pdf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1633,7 +1633,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>100833.17</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen0120243506903829501.zip::Unternehmerabrechnung - VP 120-2400000826.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 05.04. 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>28715.40</t>
+          <t>151127.70</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdihreabrechnungsunterlagen0120243506903829501.zip::Unternehmerabrechnung - VP 120-2400000990.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>165917.66</t>
+          <t>148096.04</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschrift382024zaharievmartin3.zip::Gutschrift 38-2024 Zahariev Martin 31.10.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 31-2024 Zahariev Martin 30.09.2024.pdf</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>158774.27</t>
+          <t>916.00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschrift442024zaharievmartin3.zip::Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 34-2024 Zahariev Martin 04.10.2024.pdf</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>152766.69</t>
+          <t>165917.66</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschriftapril2025zahariev_pdf.zip::gutschrift April 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 38-2024 Zahariev Martin 31.10.2024.pdf</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>170080.39</t>
+          <t>195225.85</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendengutschriftmrz2025zahariev_pdf.zip::gutschrift märz 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>143085.08</t>
+          <t>158774.27</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweismartinzaharievfe.zip::Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -1822,7 +1822,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>151127.70</t>
+          <t>101253.65</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweiszaharievjuli2024.zip::Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 66 Mai 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>46548.70</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenleistungsnachweiszaharievjuni25s.zip::Gutschrift Zahariev 74 30.06.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 71 2025 zahariev Sendungsverlust.pdf</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -1876,7 +1876,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>159310.00</t>
+          <t>152766.69</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievgutschrift4831_01_.zip::Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift April 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -1903,7 +1903,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>568.00</t>
+          <t>170080.39</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift märz 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -1930,7 +1930,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>11648.45</t>
+          <t>46548.70</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift Zahariev 74 30.06.2025.pdf</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -1957,7 +1957,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>152.50</t>
+          <t>159310.00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2038 08.01.2025 Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -1984,7 +1984,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte203608_0.zip::Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2054-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>536.00</t>
+          <t>143085.08</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2055-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>7847.85</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 55 08.03.2025.pdf</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2056-07</t>
+          <t>2035-08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>137.50</t>
+          <t>31.93</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2056 07.02.2025 Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2092,7 +2092,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2057-07</t>
+          <t>2037-08</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>11648.45</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte205407_0.zip::Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2119,7 +2119,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2070-08</t>
+          <t>2038-08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>82.50</t>
+          <t>152.50</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte207008_0.zip::Martin Zahariev Transporte 2070 08.03.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2038 08.01.2025 Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2069-08</t>
+          <t>2055-07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2763.67</t>
+          <t>7847.85</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenmartinzaharievtransporte207008_0.zip::Martin Zahariev Transporte 2069 08.03.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2173,7 +2173,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2056-07</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>504.00</t>
+          <t>137.50</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenrechnung2778zaharievhermesscanne.zip::Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2056 07.02.2025 Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2200,7 +2200,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2057-07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>79.43</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenrechnung2778zaharievhermesscanne.zip::Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2069-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>2763.67</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdperemailsendenrechnung2778zaharievhermesscanne.zip::Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2069 08.03.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2070-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>82.50</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2814 zahariev bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2070 08.03.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>10390.09</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2308,7 +2308,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2015-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>280.00</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2811 Zahariev scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2335,7 +2335,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2345,12 +2345,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>7980.00</t>
+          <t>42.43</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/fwdrechnungenaus062025.zip::Rechnung 2810 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2362,25 +2362,133 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>517.65</t>
+          <t/>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>435.00</t>
+          <t>15.50</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting/wgprqualifikationkepkdnr_60222rechnungjahresgeb.zip::20240123_60222_10160_Rechnung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>1545.27</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2766 Zahariev Hermes Sendungsverlust.pdf</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>42.50</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53652_2024 20.09.2024 10_56_50.pdf</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>

--- a/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/payroll_timeline.xlsx
+++ b/08_Reports - Доклади - Berichte/Accounting_Cash_Flow/payroll_timeline.xlsx
@@ -40,7 +40,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2022-03</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -50,12 +50,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>27.08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/02_Payroll/Lohnauswertungen_Juli_2025__copy2.pdf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -67,7 +67,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2021-04</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -77,12 +77,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 04-2025.pdf</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -94,7 +94,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2021-06</t>
+          <t>2001-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -104,12 +104,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 05-2025.pdf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -121,7 +121,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2021-12</t>
+          <t>2000-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -131,12 +131,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>18.07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/03_Employee_Payslips/Entgeltbescheinigungen 06-2025.pdf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -148,22 +148,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2022-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2494.00</t>
+          <t/>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t/>
+          <t>13.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/02-2022 #9109.pdf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -175,7 +175,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2021-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -185,12 +185,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/04-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -202,7 +202,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2021-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -212,12 +212,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>670.00</t>
+          <t>12.03</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/06-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -229,22 +229,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2021-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>517.65</t>
+          <t/>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>435.00</t>
+          <t>13.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/12-2021 #9109.pdf</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -256,12 +256,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>2494.00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -271,7 +271,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/04_Health_Insurance/Tabelle nach § 175 InsO mit Grund des Bestreitens.pdf</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -283,22 +283,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t/>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t/>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/90f3df27-1ca1-4b3a-9f1b-e33ffd37f10a.pdf</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -315,17 +315,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t/>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t/>
+          <t>670.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/05_Taxes/Rechnung_RE058675_11.08.2025.pdf</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -337,22 +337,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2002-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>31.08</t>
+          <t/>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>23.08</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/10. Nachweis von Lohnzahlungen - Bankkontoumsätze 2023.pdf</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -364,22 +364,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t/>
+          <t>517.65</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1620.17</t>
+          <t>435.00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/20240123_60222_10160_Rechnung.pdf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -391,22 +391,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t/>
+          <t>20.07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1620.17</t>
+          <t/>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102600491.PDF</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -423,7 +423,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>895.36</t>
+          <t>20.08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -433,7 +433,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102659867.PDF</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -450,7 +450,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>546.15</t>
+          <t>31.07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -460,7 +460,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102665850.PDF</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -477,7 +477,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>812.26</t>
+          <t>31.08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/KD-Nr. 550980 - Pre-Not._Nr. 6102698674.PDF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -499,22 +499,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t/>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t/>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1620.17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073-1.pdf</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -526,7 +526,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023-12</t>
+          <t/>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -536,12 +536,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>1620.17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rechnung RE211073.pdf</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -553,22 +553,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10499.90</t>
+          <t>895.36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10499.90</t>
+          <t/>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-1.PDF</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -580,22 +580,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t/>
+          <t>546.15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t/>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980-2.PDF</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -607,22 +607,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t/>
+          <t>812.26</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t/>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/06_Bank_Payments/Rücklastschrift _ Ihre KD-Nr. 550980.PDF</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -634,22 +634,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t/>
+          <t>0.20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/307538032.pdf</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/39739 - Rechnung 231128_2023 vom 28.12.2023, Aufträge 31_23, 32_23, 33_23, 34_23, 50_23, 98_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -688,22 +688,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t/>
+          <t>10499.90</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19.00</t>
+          <t>10499.90</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40579 - Rechnung 240155_2024 vom 17.02.2024, Aufträge 31_23, 33_23, 34_23, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/40850 - Rechnung 240213_2024 vom 29.01.2024, Aufträge 31_24, 32_23, 33_23, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -742,7 +742,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41261 - Rechnung 240303_2024 vom 27.03.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/41683 - Rechnung 240393_2024 vom 30.04.2024, Aufträge 31_24, 32_24, 33_24, 34_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42108 - Rechnung 240498_2024 vom 30.05.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/42585 - Rechnung 240587_2024 vom 29.06.2024, Aufträge 31_24, 33_23, 33_24, 34_24, Mandant 42303-1.pdf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -850,22 +850,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11062.00</t>
+          <t/>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>11062.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43029 - Rechnung 240697_2024 vom 31.07.2024, Aufträge 21_23, 21_24, 31_22, 31_23, 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/43617 - Rechnung 240857_2024 vom 30.08.2024, Aufträge 31_24, 32_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -904,7 +904,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>179.83</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005125.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/44458 - Rechnung 241068_2024 vom 30.10.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -931,7 +931,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -941,12 +941,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005157.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45027 - Rechnung 241185_2024 vom 29.11.2024, Aufträge 31_24, 33_24, 34_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -958,7 +958,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>568.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/45474 - Rechnung 241289_2024 vom 27.12.2024, Aufträge 21_24, 31_24, 32_24, 33_24, 34_24, 35_21, 35_24, 50_24, 98_24, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -985,22 +985,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2054-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t/>
+          <t>11062.00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>536.00</t>
+          <t>11062.00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46583 - Rechnung 250253_2025 vom 14.03.2025, Aufträge 31_25, 33_24, 34_24, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1012,7 +1012,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2058-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>536.00</t>
+          <t>19.00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/46851 - Rechnung 250303_2025 vom 31.03.2025, Aufträge 31_25, 33_25, 34_25, Mandant 42303.pdf</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1039,7 +1039,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>536.00</t>
+          <t>179.83</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005125.pdf</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1066,7 +1066,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>420.00</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/CarlundCarla_RG424005157.pdf</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1093,7 +1093,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2036-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>504.00</t>
+          <t>568.00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2036 08.01.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2054-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>30.00</t>
+          <t>536.00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2054 07.02.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2058-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>440.00</t>
+          <t>536.00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Martin Zahariev Transporte 2058 08.03.2025 Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1174,7 +1174,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>6960.00</t>
+          <t>536.00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2789 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2765 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1201,7 +1201,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>60.00</t>
+          <t>420.00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2794 Zahariev KFZ Miete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2777 Zahariev Hermes Unterstützungstouren.pdf</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>45.00</t>
+          <t>504.00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2778 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>7980.00</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2782 Zahariev Hermes Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>280.00</t>
+          <t>440.00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2788 Zahariev Hermes Scannermiete.pdf</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -1309,7 +1309,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>40.00</t>
+          <t>6960.00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2789 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1336,7 +1336,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>140.00</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2814 zahariev bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2794 Zahariev KFZ Miete.pdf</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1373,12 +1373,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1709.48</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2799 Bearbeitungsgebühr 10.06.2025 Zahariev.pdf</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1390,7 +1390,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2023-10</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>148608.05</t>
+          <t>7980.00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2810 Zahariev TF Touren.pdf</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>100833.17</t>
+          <t>280.00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000826.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2811 Zahariev scannermiete.pdf</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1444,7 +1444,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>28715.40</t>
+          <t>40.00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000990.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2813 zahariev bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>5245.59</t>
+          <t>140.00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Rechnung 2814 zahariev bekleidung.pdf</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>532.95</t>
+          <t>1709.48</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157425.pdf</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1525,7 +1525,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>148608.05</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2300157934.pdf</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2137.23</t>
+          <t>100833.17</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035414.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000826.pdf</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>511.46</t>
+          <t>28715.40</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400000990.pdf</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1606,7 +1606,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>5245.59</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Docutain Dokument.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400001108-1.pdf</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1633,7 +1633,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>532.95</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 05.04. 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400017841.pdf</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>151127.70</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400018211.pdf</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>148096.04</t>
+          <t>2137.23</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 31-2024 Zahariev Martin 30.09.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035414.pdf</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>916.00</t>
+          <t>511.46</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 34-2024 Zahariev Martin 04.10.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/08_Operating_Costs/Unternehmerabrechnung - VP 120-2400035649.pdf</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -1741,7 +1741,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>165917.66</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 38-2024 Zahariev Martin 31.10.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Docutain Dokument.pdf</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>195225.85</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 05.04. 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>158774.27</t>
+          <t>151127.70</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 24-2024 Zahariev Martin 31.07.2024.pdf</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -1822,7 +1822,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>101253.65</t>
+          <t>148096.04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 66 Mai 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 31-2024 Zahariev Martin 30.09.2024.pdf</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -1849,7 +1849,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>916.00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 71 2025 zahariev Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 34-2024 Zahariev Martin 04.10.2024.pdf</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -1876,7 +1876,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>152766.69</t>
+          <t>165917.66</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift April 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 38-2024 Zahariev Martin 31.10.2024.pdf</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -1903,7 +1903,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>170080.39</t>
+          <t>195225.85</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift märz 2025 zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 42-2024 Zahariev Martin 30.11.2024.pdf</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -1930,7 +1930,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>46548.70</t>
+          <t>158774.27</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift Zahariev 74 30.06.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift 44-2024 Zahariev Martin 31.12.2024.pdf</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -1957,7 +1957,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>159310.00</t>
+          <t>101253.65</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 66 Mai 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -1984,7 +1984,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift 71 2025 zahariev Sendungsverlust.pdf</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>143085.08</t>
+          <t>152766.69</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift April 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>170080.39</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 55 08.03.2025.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/gutschrift märz 2025 zahariev.pdf</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2075,12 +2075,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>46548.70</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Gutschrift Zahariev 74 30.06.2025.pdf</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -2092,7 +2092,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>11648.45</t>
+          <t>159310.00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 48 31.01.2025.pdf</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2119,7 +2119,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>152.50</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2038 08.01.2025 Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 51 17.02.2025.pdf</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2055-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>7847.85</t>
+          <t>143085.08</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 52 28.02.2025.pdf</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2173,7 +2173,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2056-07</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>137.50</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2056 07.02.2025 Bearbeitungsgebühr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Gutschrift 55 08.03.2025.pdf</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -2200,7 +2200,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2057-07</t>
+          <t>2035-08</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>79.43</t>
+          <t>31.93</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2035 08.01.2025 Hermes Bekleidung.pdf</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2069-08</t>
+          <t>2037-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2763.67</t>
+          <t>11648.45</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2069 08.03.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2037 08.01.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -2254,7 +2254,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2070-08</t>
+          <t>2038-08</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>82.50</t>
+          <t>152.50</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2070 08.03.2025 Sendungsverluste.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2038 08.01.2025 Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2055-07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2291,12 +2291,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>10390.09</t>
+          <t>7847.85</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2055 07.02.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -2308,7 +2308,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2015-07</t>
+          <t>2056-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2318,12 +2318,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>165.00</t>
+          <t>137.50</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2056 07.02.2025 Bearbeitungsgebühr.pdf</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -2335,7 +2335,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2057-07</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2345,12 +2345,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>42.43</t>
+          <t>79.43</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2057 07.02.2025 Hermes Bekleidung.pdf</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -2362,7 +2362,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2069-08</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>15.50</t>
+          <t>2763.67</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2069 08.03.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2070-08</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1545.27</t>
+          <t>82.50</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2766 Zahariev Hermes Sendungsverlust.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Martin Zahariev Transporte 2070 08.03.2025 Sendungsverluste.pdf</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>10390.09</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2014 vom 05.12.2024 Sendungsverlust Zahariev.pdf</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -2443,7 +2443,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2015-07</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2015 07.12.2024 Martin Zahariev.pdf</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -2470,25 +2470,160 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>42.43</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2023 vom 07.12.2024  Zahariev HERMES Bekleidung.pdf</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>15.50</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2764 Zahariev Hermes Kleidung.pdf</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>1545.27</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2766 Zahariev Hermes Sendungsverlust.pdf</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>42.50</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/09_Enrico_Forwarded/Rechnung 2767 Zahariev Hermes Bearbeitungsgebuhr.pdf</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53380_2024 13.08.2024 09_17_16.pdf</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>2024-09</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>00_INBOX - Входящи - Eingang/Accounting_Organized/11_Contribution_Lists/RE-53652_2024 20.09.2024 10_56_50.pdf</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
